--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864081</v>
+        <v>119864085</v>
       </c>
       <c r="B2" t="n">
         <v>56522</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655171</v>
+        <v>655092</v>
       </c>
       <c r="R2" t="n">
-        <v>6701535</v>
+        <v>6701484</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864082</v>
+        <v>119864080</v>
       </c>
       <c r="B3" t="n">
         <v>56522</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655126</v>
+        <v>655161</v>
       </c>
       <c r="R3" t="n">
-        <v>6701505</v>
+        <v>6701551</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864080</v>
+        <v>119864081</v>
       </c>
       <c r="B4" t="n">
         <v>56522</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655161</v>
+        <v>655171</v>
       </c>
       <c r="R4" t="n">
-        <v>6701551</v>
+        <v>6701535</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864085</v>
+        <v>119864082</v>
       </c>
       <c r="B5" t="n">
         <v>56522</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655092</v>
+        <v>655126</v>
       </c>
       <c r="R5" t="n">
-        <v>6701484</v>
+        <v>6701505</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864086</v>
+        <v>119864079</v>
       </c>
       <c r="B6" t="n">
         <v>56522</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655025</v>
+        <v>655166</v>
       </c>
       <c r="R6" t="n">
-        <v>6701400</v>
+        <v>6701567</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864079</v>
+        <v>119864086</v>
       </c>
       <c r="B7" t="n">
         <v>56522</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655166</v>
+        <v>655025</v>
       </c>
       <c r="R7" t="n">
-        <v>6701567</v>
+        <v>6701400</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864085</v>
+        <v>119864081</v>
       </c>
       <c r="B2" t="n">
         <v>56522</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655092</v>
+        <v>655171</v>
       </c>
       <c r="R2" t="n">
-        <v>6701484</v>
+        <v>6701535</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864081</v>
+        <v>119864079</v>
       </c>
       <c r="B4" t="n">
         <v>56522</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655171</v>
+        <v>655166</v>
       </c>
       <c r="R4" t="n">
-        <v>6701535</v>
+        <v>6701567</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864079</v>
+        <v>119864083</v>
       </c>
       <c r="B6" t="n">
         <v>56522</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655166</v>
+        <v>655098</v>
       </c>
       <c r="R6" t="n">
-        <v>6701567</v>
+        <v>6701489</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864086</v>
+        <v>119864085</v>
       </c>
       <c r="B7" t="n">
         <v>56522</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655025</v>
+        <v>655092</v>
       </c>
       <c r="R7" t="n">
-        <v>6701400</v>
+        <v>6701484</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864083</v>
+        <v>119864086</v>
       </c>
       <c r="B8" t="n">
         <v>56522</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655098</v>
+        <v>655025</v>
       </c>
       <c r="R8" t="n">
-        <v>6701489</v>
+        <v>6701400</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864081</v>
+        <v>119864085</v>
       </c>
       <c r="B2" t="n">
         <v>56522</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655171</v>
+        <v>655092</v>
       </c>
       <c r="R2" t="n">
-        <v>6701535</v>
+        <v>6701484</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864080</v>
+        <v>119864082</v>
       </c>
       <c r="B3" t="n">
         <v>56522</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655161</v>
+        <v>655126</v>
       </c>
       <c r="R3" t="n">
-        <v>6701551</v>
+        <v>6701505</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864082</v>
+        <v>119864081</v>
       </c>
       <c r="B5" t="n">
         <v>56522</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655126</v>
+        <v>655171</v>
       </c>
       <c r="R5" t="n">
-        <v>6701505</v>
+        <v>6701535</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864083</v>
+        <v>119864086</v>
       </c>
       <c r="B6" t="n">
         <v>56522</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655098</v>
+        <v>655025</v>
       </c>
       <c r="R6" t="n">
-        <v>6701489</v>
+        <v>6701400</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864085</v>
+        <v>119864083</v>
       </c>
       <c r="B7" t="n">
         <v>56522</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655092</v>
+        <v>655098</v>
       </c>
       <c r="R7" t="n">
-        <v>6701484</v>
+        <v>6701489</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864086</v>
+        <v>119864080</v>
       </c>
       <c r="B8" t="n">
         <v>56522</v>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655025</v>
+        <v>655161</v>
       </c>
       <c r="R8" t="n">
-        <v>6701400</v>
+        <v>6701551</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864085</v>
+        <v>119864082</v>
       </c>
       <c r="B2" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655092</v>
+        <v>655126</v>
       </c>
       <c r="R2" t="n">
-        <v>6701484</v>
+        <v>6701505</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864082</v>
+        <v>119864086</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655126</v>
+        <v>655025</v>
       </c>
       <c r="R3" t="n">
-        <v>6701505</v>
+        <v>6701400</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>119864079</v>
       </c>
       <c r="B4" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>119864081</v>
       </c>
       <c r="B5" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864086</v>
+        <v>119864080</v>
       </c>
       <c r="B6" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655025</v>
+        <v>655161</v>
       </c>
       <c r="R6" t="n">
-        <v>6701400</v>
+        <v>6701551</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,7 +1303,7 @@
         <v>119864083</v>
       </c>
       <c r="B7" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864080</v>
+        <v>119864085</v>
       </c>
       <c r="B8" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655161</v>
+        <v>655092</v>
       </c>
       <c r="R8" t="n">
-        <v>6701551</v>
+        <v>6701484</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864082</v>
+        <v>119864081</v>
       </c>
       <c r="B2" t="n">
         <v>56532</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655126</v>
+        <v>655171</v>
       </c>
       <c r="R2" t="n">
-        <v>6701505</v>
+        <v>6701535</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864086</v>
+        <v>119864085</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655025</v>
+        <v>655092</v>
       </c>
       <c r="R3" t="n">
-        <v>6701400</v>
+        <v>6701484</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864079</v>
+        <v>119864080</v>
       </c>
       <c r="B4" t="n">
         <v>56532</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655166</v>
+        <v>655161</v>
       </c>
       <c r="R4" t="n">
-        <v>6701567</v>
+        <v>6701551</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864081</v>
+        <v>119864086</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655171</v>
+        <v>655025</v>
       </c>
       <c r="R5" t="n">
-        <v>6701535</v>
+        <v>6701400</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864080</v>
+        <v>119864079</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655161</v>
+        <v>655166</v>
       </c>
       <c r="R6" t="n">
-        <v>6701551</v>
+        <v>6701567</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864083</v>
+        <v>119864082</v>
       </c>
       <c r="B7" t="n">
         <v>56532</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655098</v>
+        <v>655126</v>
       </c>
       <c r="R7" t="n">
-        <v>6701489</v>
+        <v>6701505</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864085</v>
+        <v>119864083</v>
       </c>
       <c r="B8" t="n">
         <v>56532</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655092</v>
+        <v>655098</v>
       </c>
       <c r="R8" t="n">
-        <v>6701484</v>
+        <v>6701489</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864085</v>
+        <v>119864082</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655092</v>
+        <v>655126</v>
       </c>
       <c r="R3" t="n">
-        <v>6701484</v>
+        <v>6701505</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864086</v>
+        <v>119864085</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655025</v>
+        <v>655092</v>
       </c>
       <c r="R5" t="n">
-        <v>6701400</v>
+        <v>6701484</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864079</v>
+        <v>119864086</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655166</v>
+        <v>655025</v>
       </c>
       <c r="R6" t="n">
-        <v>6701567</v>
+        <v>6701400</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864082</v>
+        <v>119864079</v>
       </c>
       <c r="B7" t="n">
         <v>56532</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655126</v>
+        <v>655166</v>
       </c>
       <c r="R7" t="n">
-        <v>6701505</v>
+        <v>6701567</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864081</v>
+        <v>119864085</v>
       </c>
       <c r="B2" t="n">
         <v>56532</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655171</v>
+        <v>655092</v>
       </c>
       <c r="R2" t="n">
-        <v>6701535</v>
+        <v>6701484</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864082</v>
+        <v>119864083</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655126</v>
+        <v>655098</v>
       </c>
       <c r="R3" t="n">
-        <v>6701505</v>
+        <v>6701489</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864085</v>
+        <v>119864086</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655092</v>
+        <v>655025</v>
       </c>
       <c r="R5" t="n">
-        <v>6701484</v>
+        <v>6701400</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864086</v>
+        <v>119864082</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655025</v>
+        <v>655126</v>
       </c>
       <c r="R6" t="n">
-        <v>6701400</v>
+        <v>6701505</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864083</v>
+        <v>119864081</v>
       </c>
       <c r="B8" t="n">
         <v>56532</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655098</v>
+        <v>655171</v>
       </c>
       <c r="R8" t="n">
-        <v>6701489</v>
+        <v>6701535</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50442-2021 artfynd.xlsx
+++ b/artfynd/A 50442-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864085</v>
+        <v>119864079</v>
       </c>
       <c r="B2" t="n">
         <v>56532</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655092</v>
+        <v>655166</v>
       </c>
       <c r="R2" t="n">
-        <v>6701484</v>
+        <v>6701567</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864083</v>
+        <v>119864080</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655098</v>
+        <v>655161</v>
       </c>
       <c r="R3" t="n">
-        <v>6701489</v>
+        <v>6701551</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864080</v>
+        <v>119864081</v>
       </c>
       <c r="B4" t="n">
         <v>56532</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655161</v>
+        <v>655171</v>
       </c>
       <c r="R4" t="n">
-        <v>6701551</v>
+        <v>6701535</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864086</v>
+        <v>119864083</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655025</v>
+        <v>655098</v>
       </c>
       <c r="R5" t="n">
-        <v>6701400</v>
+        <v>6701489</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864082</v>
+        <v>119864085</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655126</v>
+        <v>655092</v>
       </c>
       <c r="R6" t="n">
-        <v>6701505</v>
+        <v>6701484</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864079</v>
+        <v>119864082</v>
       </c>
       <c r="B7" t="n">
         <v>56532</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655166</v>
+        <v>655126</v>
       </c>
       <c r="R7" t="n">
-        <v>6701567</v>
+        <v>6701505</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864081</v>
+        <v>119864086</v>
       </c>
       <c r="B8" t="n">
         <v>56532</v>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655171</v>
+        <v>655025</v>
       </c>
       <c r="R8" t="n">
-        <v>6701535</v>
+        <v>6701400</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
